--- a/Data/Input/debugProcesses.xlsx
+++ b/Data/Input/debugProcesses.xlsx
@@ -482,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.35">
@@ -490,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.35">
@@ -501,10 +501,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.35">
@@ -512,10 +512,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.35">
@@ -523,10 +523,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
